--- a/data/inventario.xlsx
+++ b/data/inventario.xlsx
@@ -1,28 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8C7B4BE-E559-42F3-B399-A4A690CBF3E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="Pedidos" sheetId="2" r:id="rId1"/>
-    <sheet name="CUSTODIOS" sheetId="3" r:id="rId2"/>
-    <sheet name="vehiculos" sheetId="4" r:id="rId3"/>
+    <sheet r:id="rId1" sheetId="1" name="Pedidos"/>
+    <sheet r:id="rId2" sheetId="2" name="CUSTODIOS"/>
+    <sheet r:id="rId3" sheetId="3" name="vehiculos"/>
   </sheets>
-  <calcPr calcId="171027"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
+  <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="69">
+  <si>
+    <t>Placa</t>
+  </si>
+  <si>
+    <t>GPR-1234</t>
+  </si>
+  <si>
+    <t>GTR-4569</t>
+  </si>
   <si>
     <t>Nombre</t>
   </si>
@@ -75,15 +78,6 @@
     <t>0961142511</t>
   </si>
   <si>
-    <t>Placa</t>
-  </si>
-  <si>
-    <t>GPR-1234</t>
-  </si>
-  <si>
-    <t>gtr-4569</t>
-  </si>
-  <si>
     <t>ID Pedido</t>
   </si>
   <si>
@@ -139,9 +133,6 @@
   </si>
   <si>
     <t>Externa</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>oscar</t>
@@ -237,7 +228,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+  <numFmts count="0"/>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -267,57 +259,60 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="3">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" builtinId="0" name="Normal"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{469C3232-17E6-4695-91C5-62C73411BF0D}" name="Tabla2" displayName="Tabla2" ref="A1:M7" totalsRowShown="0">
-  <autoFilter ref="A1:M7" xr:uid="{469C3232-17E6-4695-91C5-62C73411BF0D}"/>
-  <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{FBA83D38-B862-449D-B2ED-13C42B5AF49D}" name="ID Pedido"/>
-    <tableColumn id="2" xr3:uid="{2B9F8ADF-511F-422C-AF49-BE120A06BA88}" name="Fecha"/>
-    <tableColumn id="3" xr3:uid="{009EE110-2484-4491-AC62-7DBBC7F790FC}" name="Cliente"/>
-    <tableColumn id="4" xr3:uid="{247E2D7A-C10C-4623-84C8-C29888C53E29}" name="Lugar"/>
-    <tableColumn id="5" xr3:uid="{FA9DACB1-96A5-49D9-BE4E-EE63C9298A21}" name="Destino"/>
-    <tableColumn id="6" xr3:uid="{2C715BA3-78EE-42C2-93DB-98048025E433}" name="Tipo de Custodia"/>
-    <tableColumn id="7" xr3:uid="{A08594BC-FD9B-4E71-802D-A2224B60C9D8}" name="# Guía"/>
-    <tableColumn id="8" xr3:uid="{1D159707-44E8-454C-A005-54A074414D8A}" name="Jefe Patrulla"/>
-    <tableColumn id="9" xr3:uid="{14417D8F-58DB-4437-A115-49BE183084EA}" name="Custodio 2"/>
-    <tableColumn id="10" xr3:uid="{C6054916-57B9-4656-BA4C-886F643E6686}" name="Custodio 3"/>
-    <tableColumn id="11" xr3:uid="{35596E81-5A59-410B-8A93-E833C518871C}" name="Placa Vehículo"/>
-    <tableColumn id="12" xr3:uid="{BB46B959-7590-42EA-B89F-123987DDF0A6}" name="Hora"/>
-    <tableColumn id="13" xr3:uid="{FA0DE4B5-8FB7-4E38-A204-E950DAED1327}" name="Estado"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:D5" displayName="Tabla1" name="Tabla1" id="1" totalsRowShown="0">
+  <autoFilter ref="A1:D5"/>
+  <tableColumns count="4">
+    <tableColumn name="Nombre" id="1"/>
+    <tableColumn name="Apellidos" id="2"/>
+    <tableColumn name="CI" id="3"/>
+    <tableColumn name="Telefono" id="4"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight1" showColumnStripes="0" showRowStripes="1" showLastColumn="0" showFirstColumn="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{96DD4C88-CCE2-45DD-9E07-73721712C767}" name="Tabla1" displayName="Tabla1" ref="A1:D5" totalsRowShown="0">
-  <autoFilter ref="A1:D5" xr:uid="{96DD4C88-CCE2-45DD-9E07-73721712C767}"/>
-  <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{1B64770C-02A9-4AFC-82D4-9B54F33369AA}" name="Nombre"/>
-    <tableColumn id="2" xr3:uid="{E05B03E0-719E-402B-974C-45E2F6BA42F7}" name="Apellidos"/>
-    <tableColumn id="3" xr3:uid="{AE92E665-6949-4C85-B5C1-33346EBF7184}" name="CI"/>
-    <tableColumn id="4" xr3:uid="{C65A4DB9-5A89-4086-8AB9-6085805B0A73}" name="Telefono"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:M7" displayName="Tabla2" name="Tabla2" id="2" totalsRowShown="0">
+  <autoFilter ref="A1:M7"/>
+  <tableColumns count="13">
+    <tableColumn name="ID Pedido" id="1"/>
+    <tableColumn name="Fecha" id="2"/>
+    <tableColumn name="Cliente" id="3"/>
+    <tableColumn name="Lugar" id="4"/>
+    <tableColumn name="Destino" id="5"/>
+    <tableColumn name="Tipo de Custodia" id="6"/>
+    <tableColumn name="# Guía" id="7"/>
+    <tableColumn name="Jefe Patrulla" id="8"/>
+    <tableColumn name="Custodio 2" id="9"/>
+    <tableColumn name="Custodio 3" id="10"/>
+    <tableColumn name="Placa Vehículo" id="11"/>
+    <tableColumn name="Hora" id="12"/>
+    <tableColumn name="Estado" id="13"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight1" showColumnStripes="0" showRowStripes="1" showLastColumn="0" showFirstColumn="0"/>
 </table>
 </file>
 
@@ -326,10 +321,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -367,71 +362,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Times New Roman" script="Arab"/>
+        <a:font typeface="Times New Roman" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="MoolBoran" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Times New Roman" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Arial" script="Arab"/>
+        <a:font typeface="Arial" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="DaunPenh" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Arial" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -455,50 +450,53 @@
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
                 <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
+                <a:tint val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
           <a:solidFill>
             <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
+              <a:shade val="9500"/>
               <a:satMod val="105000"/>
             </a:schemeClr>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -508,7 +506,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -517,7 +515,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -526,7 +524,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -534,10 +532,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
+              <a:rot rev="0" lon="0" lat="0"/>
             </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
+            <a:lightRig dir="t" rig="threePt">
+              <a:rot rev="1200000" lon="0" lat="0"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -566,7 +564,7 @@
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
+                <a:tint val="20000"/>
                 <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
@@ -579,13 +577,12 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
                 <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
+                <a:tint val="80000"/>
                 <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
@@ -597,360 +594,289 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+  </sheetPr>
   <dimension ref="A1:M7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.33203125" customWidth="1"/>
-    <col min="2" max="2" width="11.33203125" customWidth="1"/>
-    <col min="3" max="3" width="12.44140625" customWidth="1"/>
-    <col min="4" max="4" width="13.5546875" customWidth="1"/>
-    <col min="5" max="5" width="15.109375" customWidth="1"/>
-    <col min="6" max="6" width="12.6640625" customWidth="1"/>
-    <col min="7" max="7" width="8.109375" customWidth="1"/>
-    <col min="8" max="8" width="15.6640625" customWidth="1"/>
-    <col min="9" max="9" width="16" customWidth="1"/>
-    <col min="10" max="10" width="17.6640625" customWidth="1"/>
-    <col min="11" max="11" width="12.77734375" customWidth="1"/>
-    <col min="12" max="12" width="6.88671875" customWidth="1"/>
-    <col min="13" max="13" width="13.88671875" customWidth="1"/>
+    <col min="1" max="1" style="2" width="6.2907142857142855" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="2" width="11.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="2" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="2" width="15.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="2" width="12.719285714285713" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="2" width="8.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="2" width="15.719285714285713" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="2" width="16.005" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="2" width="17.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="2" width="12.719285714285713" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="2" width="6.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="2" width="13.862142857142858" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+      <c r="A1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="A2" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="1"/>
+      <c r="H2" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L2" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="K2" t="s">
-        <v>18</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="M2" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="M2" t="s">
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="A3" s="1" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="B3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B3" t="s">
+      <c r="D3" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="A4" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+      <c r="A5" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+      <c r="A6" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+      <c r="A7" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="C7" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="M7" s="1" t="s">
         <v>48</v>
-      </c>
-      <c r="F3" t="s">
-        <v>38</v>
-      </c>
-      <c r="G3" t="s">
-        <v>39</v>
-      </c>
-      <c r="H3" t="s">
-        <v>39</v>
-      </c>
-      <c r="I3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J3" t="s">
-        <v>39</v>
-      </c>
-      <c r="K3" t="s">
-        <v>39</v>
-      </c>
-      <c r="L3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G4" t="s">
-        <v>56</v>
-      </c>
-      <c r="H4" t="s">
-        <v>39</v>
-      </c>
-      <c r="I4" t="s">
-        <v>39</v>
-      </c>
-      <c r="J4" t="s">
-        <v>39</v>
-      </c>
-      <c r="K4" t="s">
-        <v>39</v>
-      </c>
-      <c r="L4" t="s">
-        <v>39</v>
-      </c>
-      <c r="M4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>58</v>
-      </c>
-      <c r="B5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E5" t="s">
-        <v>61</v>
-      </c>
-      <c r="F5" t="s">
-        <v>55</v>
-      </c>
-      <c r="G5" t="s">
-        <v>39</v>
-      </c>
-      <c r="H5" t="s">
-        <v>40</v>
-      </c>
-      <c r="I5" t="s">
-        <v>41</v>
-      </c>
-      <c r="J5" t="s">
-        <v>42</v>
-      </c>
-      <c r="K5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L5" t="s">
-        <v>39</v>
-      </c>
-      <c r="M5" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>62</v>
-      </c>
-      <c r="B6" t="s">
-        <v>59</v>
-      </c>
-      <c r="C6" t="s">
-        <v>60</v>
-      </c>
-      <c r="D6" t="s">
-        <v>36</v>
-      </c>
-      <c r="E6" t="s">
-        <v>37</v>
-      </c>
-      <c r="F6" t="s">
-        <v>38</v>
-      </c>
-      <c r="G6" t="s">
-        <v>39</v>
-      </c>
-      <c r="H6" t="s">
-        <v>12</v>
-      </c>
-      <c r="I6" t="s">
-        <v>12</v>
-      </c>
-      <c r="J6" t="s">
-        <v>12</v>
-      </c>
-      <c r="K6" t="s">
-        <v>18</v>
-      </c>
-      <c r="L6" t="s">
-        <v>39</v>
-      </c>
-      <c r="M6" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C7" t="s">
-        <v>64</v>
-      </c>
-      <c r="D7" t="s">
-        <v>65</v>
-      </c>
-      <c r="E7" t="s">
-        <v>66</v>
-      </c>
-      <c r="F7" t="s">
-        <v>38</v>
-      </c>
-      <c r="G7" t="s">
-        <v>39</v>
-      </c>
-      <c r="H7" t="s">
-        <v>67</v>
-      </c>
-      <c r="I7" t="s">
-        <v>41</v>
-      </c>
-      <c r="J7" t="s">
-        <v>68</v>
-      </c>
-      <c r="K7" t="s">
-        <v>18</v>
-      </c>
-      <c r="L7" t="s">
-        <v>69</v>
-      </c>
-      <c r="M7" t="s">
-        <v>49</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
@@ -958,79 +884,85 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+  </sheetPr>
   <dimension ref="A1:D5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.88671875" customWidth="1"/>
-    <col min="2" max="2" width="15.5546875" customWidth="1"/>
-    <col min="3" max="4" width="18.44140625" customWidth="1"/>
+    <col min="1" max="1" style="2" width="19.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="2" width="15.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="2" width="18.433571428571426" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="2" width="18.433571428571426" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+      <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="B1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D2" t="s">
+    </row>
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="B2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D3" t="s">
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="C3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B5" t="s">
+      <c r="D3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C5" t="s">
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D5" t="s">
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+      <c r="A5" s="1" t="s">
         <v>16</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
@@ -1038,27 +970,32 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+  </sheetPr>
   <dimension ref="A1:A3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>19</v>
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
--- a/data/inventario.xlsx
+++ b/data/inventario.xlsx
@@ -1,242 +1,248 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
     <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet r:id="rId1" sheetId="1" name="Pedidos"/>
-    <sheet r:id="rId2" sheetId="2" name="CUSTODIOS"/>
-    <sheet r:id="rId3" sheetId="3" name="vehiculos"/>
+    <sheet sheetId="1" name="Pedidos" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="CUSTODIOS" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="vehiculos" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="Rutas" state="visible" r:id="rId7"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="71">
+  <si>
+    <t>ID Pedido</t>
+  </si>
+  <si>
+    <t>Fecha</t>
+  </si>
+  <si>
+    <t>Cliente</t>
+  </si>
+  <si>
+    <t>Lugar</t>
+  </si>
+  <si>
+    <t>Destino</t>
+  </si>
+  <si>
+    <t>Tipo de Custodia</t>
+  </si>
+  <si>
+    <t># Guía</t>
+  </si>
+  <si>
+    <t>Jefe Patrulla</t>
+  </si>
+  <si>
+    <t>Custodio 2</t>
+  </si>
+  <si>
+    <t>Custodio 3</t>
+  </si>
+  <si>
+    <t>Placa Vehículo</t>
+  </si>
+  <si>
+    <t>Hora</t>
+  </si>
+  <si>
+    <t>Estado</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>2026-03-24</t>
+  </si>
+  <si>
+    <t>ASUS</t>
+  </si>
+  <si>
+    <t>GYE</t>
+  </si>
+  <si>
+    <t>UIO</t>
+  </si>
+  <si>
+    <t>Externa</t>
+  </si>
+  <si>
+    <t>oscar</t>
+  </si>
+  <si>
+    <t>Juan Perez</t>
+  </si>
+  <si>
+    <t>david</t>
+  </si>
+  <si>
+    <t>GPR-1234</t>
+  </si>
+  <si>
+    <t>14:00</t>
+  </si>
+  <si>
+    <t>EN PROCESO</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>TESTEDIT</t>
+  </si>
+  <si>
+    <t>LUGAR X2</t>
+  </si>
+  <si>
+    <t>DEST2</t>
+  </si>
+  <si>
+    <t>PENDIENTE</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>2026-03-26</t>
+  </si>
+  <si>
+    <t>TESTE2</t>
+  </si>
+  <si>
+    <t>LUG2X</t>
+  </si>
+  <si>
+    <t>D2X</t>
+  </si>
+  <si>
+    <t>Interna</t>
+  </si>
+  <si>
+    <t>456</t>
+  </si>
+  <si>
+    <t>FINALIZADO</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>2026-03-25</t>
+  </si>
+  <si>
+    <t>REVIT</t>
+  </si>
+  <si>
+    <t>BODEGA DAULE</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>X CONFIRMAR</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>CARGOLAN</t>
+  </si>
+  <si>
+    <t>Pto.Contecom</t>
+  </si>
+  <si>
+    <t>Cuenca</t>
+  </si>
+  <si>
+    <t>Oscar Guachamin</t>
+  </si>
+  <si>
+    <t>David Sanchez</t>
+  </si>
+  <si>
+    <t>03:00</t>
+  </si>
+  <si>
+    <t>Nombre</t>
+  </si>
+  <si>
+    <t>Apellidos</t>
+  </si>
+  <si>
+    <t>CI</t>
+  </si>
+  <si>
+    <t>Telefono</t>
+  </si>
+  <si>
+    <t>Juan</t>
+  </si>
+  <si>
+    <t>Perez</t>
+  </si>
+  <si>
+    <t>0123456789</t>
+  </si>
+  <si>
+    <t>7894561230</t>
+  </si>
+  <si>
+    <t>David</t>
+  </si>
+  <si>
+    <t>Sanchez</t>
+  </si>
+  <si>
+    <t>9632587410</t>
+  </si>
+  <si>
+    <t>7410258963</t>
+  </si>
+  <si>
+    <t>Oscar</t>
+  </si>
+  <si>
+    <t>Guachamin</t>
+  </si>
+  <si>
+    <t>0923522866</t>
+  </si>
+  <si>
+    <t>0961142511</t>
+  </si>
   <si>
     <t>Placa</t>
   </si>
   <si>
-    <t>GPR-1234</t>
-  </si>
-  <si>
     <t>GTR-4569</t>
   </si>
   <si>
-    <t>Nombre</t>
-  </si>
-  <si>
-    <t>Apellidos</t>
-  </si>
-  <si>
-    <t>CI</t>
-  </si>
-  <si>
-    <t>Telefono</t>
-  </si>
-  <si>
-    <t>Juan</t>
-  </si>
-  <si>
-    <t>Perez</t>
-  </si>
-  <si>
-    <t>0123456789</t>
-  </si>
-  <si>
-    <t>7894561230</t>
-  </si>
-  <si>
-    <t>David</t>
-  </si>
-  <si>
-    <t>Sanchez</t>
-  </si>
-  <si>
-    <t>9632587410</t>
-  </si>
-  <si>
-    <t>7410258963</t>
-  </si>
-  <si>
-    <t>X CONFIRMAR</t>
-  </si>
-  <si>
-    <t>Oscar</t>
-  </si>
-  <si>
-    <t>Guachamin</t>
-  </si>
-  <si>
-    <t>0923522866</t>
-  </si>
-  <si>
-    <t>0961142511</t>
-  </si>
-  <si>
-    <t>ID Pedido</t>
-  </si>
-  <si>
-    <t>Fecha</t>
-  </si>
-  <si>
-    <t>Cliente</t>
-  </si>
-  <si>
-    <t>Lugar</t>
-  </si>
-  <si>
-    <t>Destino</t>
-  </si>
-  <si>
-    <t>Tipo de Custodia</t>
-  </si>
-  <si>
-    <t># Guía</t>
-  </si>
-  <si>
-    <t>Jefe Patrulla</t>
-  </si>
-  <si>
-    <t>Custodio 2</t>
-  </si>
-  <si>
-    <t>Custodio 3</t>
-  </si>
-  <si>
-    <t>Placa Vehículo</t>
-  </si>
-  <si>
-    <t>Hora</t>
-  </si>
-  <si>
-    <t>Estado</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>2026-03-24</t>
-  </si>
-  <si>
-    <t>ASUS</t>
-  </si>
-  <si>
-    <t>GYE</t>
-  </si>
-  <si>
-    <t>UIO</t>
-  </si>
-  <si>
-    <t>Externa</t>
-  </si>
-  <si>
-    <t>oscar</t>
-  </si>
-  <si>
-    <t>Juan Perez</t>
-  </si>
-  <si>
-    <t>david</t>
-  </si>
-  <si>
-    <t>14:00</t>
-  </si>
-  <si>
-    <t>EN PROCESO</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>TESTEDIT</t>
-  </si>
-  <si>
-    <t>LUGAR X2</t>
-  </si>
-  <si>
-    <t>DEST2</t>
-  </si>
-  <si>
-    <t>PENDIENTE</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>2026-03-26</t>
-  </si>
-  <si>
-    <t>TESTE2</t>
-  </si>
-  <si>
-    <t>LUG2X</t>
-  </si>
-  <si>
-    <t>D2X</t>
-  </si>
-  <si>
-    <t>Interna</t>
-  </si>
-  <si>
-    <t>456</t>
-  </si>
-  <si>
-    <t>FINALIZADO</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>2026-03-25</t>
-  </si>
-  <si>
-    <t>REVIT</t>
-  </si>
-  <si>
-    <t>BODEGA DAULE</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>CARGOLAN</t>
-  </si>
-  <si>
-    <t>Pto.Contecom</t>
-  </si>
-  <si>
-    <t>Cuenca</t>
-  </si>
-  <si>
-    <t>Oscar Guachamin</t>
-  </si>
-  <si>
-    <t>David Sanchez</t>
-  </si>
-  <si>
-    <t>03:00</t>
+    <t>Ruta</t>
+  </si>
+  <si>
+    <t>RUTA-PRUEBA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -259,60 +265,77 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0" name="Normal"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:D5" displayName="Tabla1" name="Tabla1" id="1" totalsRowShown="0">
-  <autoFilter ref="A1:D5"/>
-  <tableColumns count="4">
-    <tableColumn name="Nombre" id="1"/>
-    <tableColumn name="Apellidos" id="2"/>
-    <tableColumn name="CI" id="3"/>
-    <tableColumn name="Telefono" id="4"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" name="Tabla2" displayName="Tabla2" ref="A1:M7" totalsRowShown="1" headerRowCount="0">
+  <autoFilter ref="A1:M7">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+    <filterColumn colId="3" hiddenButton="1"/>
+    <filterColumn colId="4" hiddenButton="1"/>
+    <filterColumn colId="5" hiddenButton="1"/>
+    <filterColumn colId="6" hiddenButton="1"/>
+    <filterColumn colId="7" hiddenButton="1"/>
+    <filterColumn colId="8" hiddenButton="1"/>
+    <filterColumn colId="9" hiddenButton="1"/>
+    <filterColumn colId="10" hiddenButton="1"/>
+    <filterColumn colId="11" hiddenButton="1"/>
+    <filterColumn colId="12" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="13">
+    <tableColumn id="1" name="ID Pedido"/>
+    <tableColumn id="2" name="Fecha"/>
+    <tableColumn id="3" name="Cliente"/>
+    <tableColumn id="4" name="Lugar"/>
+    <tableColumn id="5" name="Destino"/>
+    <tableColumn id="6" name="Tipo de Custodia"/>
+    <tableColumn id="7" name="# Guía"/>
+    <tableColumn id="8" name="Jefe Patrulla"/>
+    <tableColumn id="9" name="Custodio 2"/>
+    <tableColumn id="10" name="Custodio 3"/>
+    <tableColumn id="11" name="Placa Vehículo"/>
+    <tableColumn id="12" name="Hora"/>
+    <tableColumn id="13" name="Estado"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showColumnStripes="0" showRowStripes="1" showLastColumn="0" showFirstColumn="0"/>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:M7" displayName="Tabla2" name="Tabla2" id="2" totalsRowShown="0">
-  <autoFilter ref="A1:M7"/>
-  <tableColumns count="13">
-    <tableColumn name="ID Pedido" id="1"/>
-    <tableColumn name="Fecha" id="2"/>
-    <tableColumn name="Cliente" id="3"/>
-    <tableColumn name="Lugar" id="4"/>
-    <tableColumn name="Destino" id="5"/>
-    <tableColumn name="Tipo de Custodia" id="6"/>
-    <tableColumn name="# Guía" id="7"/>
-    <tableColumn name="Jefe Patrulla" id="8"/>
-    <tableColumn name="Custodio 2" id="9"/>
-    <tableColumn name="Custodio 3" id="10"/>
-    <tableColumn name="Placa Vehículo" id="11"/>
-    <tableColumn name="Hora" id="12"/>
-    <tableColumn name="Estado" id="13"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" name="Tabla1" displayName="Tabla1" ref="A1:D5" totalsRowShown="1" headerRowCount="0">
+  <autoFilter ref="A1:D5">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+    <filterColumn colId="3" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="4">
+    <tableColumn id="1" name="Nombre"/>
+    <tableColumn id="2" name="Apellidos"/>
+    <tableColumn id="3" name="CI"/>
+    <tableColumn id="4" name="Telefono"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showColumnStripes="0" showRowStripes="1" showLastColumn="0" showFirstColumn="0"/>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -605,121 +628,121 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="2" width="6.2907142857142855" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="2" width="11.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="2" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="2" width="15.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="2" width="12.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="2" width="8.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="2" width="15.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="2" width="16.005" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="2" width="17.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="2" width="12.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="2" width="6.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="2" width="13.862142857142858" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="6.2907142857142855" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.290714285714287" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.43357142857143" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.576428571428572" style="1" customWidth="1"/>
+    <col min="5" max="5" width="15.147857142857141" style="1" customWidth="1"/>
+    <col min="6" max="6" width="12.719285714285713" style="1" customWidth="1"/>
+    <col min="7" max="7" width="8.147857142857141" style="1" customWidth="1"/>
+    <col min="8" max="8" width="15.719285714285713" style="1" customWidth="1"/>
+    <col min="9" max="9" width="16.005" style="1" customWidth="1"/>
+    <col min="10" max="10" width="17.719285714285714" style="1" customWidth="1"/>
+    <col min="11" max="11" width="12.719285714285713" style="1" customWidth="1"/>
+    <col min="12" max="12" width="6.862142857142857" style="1" customWidth="1"/>
+    <col min="13" max="13" width="13.862142857142858" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row r="1" ht="18.75" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" ht="18.75" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="G2" s="1"/>
       <c r="H2" s="1" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" ht="18.75" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
@@ -728,30 +751,30 @@
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" ht="18.75" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
@@ -759,120 +782,120 @@
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
       <c r="M4" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" ht="18.75" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="G5" s="1"/>
       <c r="H5" s="1" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="L5" s="1"/>
       <c r="M5" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" ht="18.75" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="G6" s="1"/>
       <c r="H6" s="1" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="L6" s="1"/>
       <c r="M6" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" ht="18.75" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="G7" s="1"/>
       <c r="H7" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -889,76 +912,75 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="2" width="19.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="2" width="15.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="2" width="18.433571428571426" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="2" width="18.433571428571426" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="19.862142857142857" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.576428571428572" style="1" customWidth="1"/>
+    <col min="3" max="4" width="18.433571428571426" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row r="1" ht="18.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" ht="18.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
+        <v>56</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>9</v>
+        <v>57</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3" ht="18.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>59</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>13</v>
+        <v>61</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="4" ht="18.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+    <row r="5" ht="18.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>16</v>
+        <v>63</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>19</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -975,27 +997,78 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="13.576428571428572" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row r="1" ht="18.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="2" ht="18.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" ht="18.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
 </file>
--- a/data/inventario.xlsx
+++ b/data/inventario.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="73">
   <si>
     <t>ID Pedido</t>
   </si>
@@ -230,6 +230,12 @@
   </si>
   <si>
     <t>RUTA-PRUEBA</t>
+  </si>
+  <si>
+    <t>RUTA-PRUEBA-AUTO</t>
+  </si>
+  <si>
+    <t>Gye-Cuenca</t>
   </si>
 </sst>
 </file>
@@ -265,9 +271,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -630,271 +635,254 @@
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.2907142857142855" style="1" customWidth="1"/>
-    <col min="2" max="2" width="11.290714285714287" style="1" customWidth="1"/>
-    <col min="3" max="3" width="12.43357142857143" style="1" customWidth="1"/>
-    <col min="4" max="4" width="13.576428571428572" style="1" customWidth="1"/>
-    <col min="5" max="5" width="15.147857142857141" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12.719285714285713" style="1" customWidth="1"/>
-    <col min="7" max="7" width="8.147857142857141" style="1" customWidth="1"/>
-    <col min="8" max="8" width="15.719285714285713" style="1" customWidth="1"/>
-    <col min="9" max="9" width="16.005" style="1" customWidth="1"/>
-    <col min="10" max="10" width="17.719285714285714" style="1" customWidth="1"/>
-    <col min="11" max="11" width="12.719285714285713" style="1" customWidth="1"/>
-    <col min="12" max="12" width="6.862142857142857" style="1" customWidth="1"/>
-    <col min="13" max="13" width="13.862142857142858" style="1" customWidth="1"/>
+    <col min="1" max="1" width="6.2907142857142855" customWidth="1"/>
+    <col min="2" max="2" width="11.290714285714287" customWidth="1"/>
+    <col min="3" max="3" width="12.43357142857143" customWidth="1"/>
+    <col min="4" max="4" width="13.576428571428572" customWidth="1"/>
+    <col min="5" max="5" width="15.147857142857141" customWidth="1"/>
+    <col min="6" max="6" width="12.719285714285713" customWidth="1"/>
+    <col min="7" max="7" width="8.147857142857141" customWidth="1"/>
+    <col min="8" max="8" width="15.719285714285713" customWidth="1"/>
+    <col min="9" max="9" width="16.005" customWidth="1"/>
+    <col min="10" max="10" width="17.719285714285714" customWidth="1"/>
+    <col min="11" max="11" width="12.719285714285713" customWidth="1"/>
+    <col min="12" max="12" width="6.862142857142857" customWidth="1"/>
+    <col min="13" max="13" width="13.862142857142858" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" t="s">
         <v>18</v>
       </c>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1" t="s">
+      <c r="H2" t="s">
         <v>19</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" t="s">
         <v>20</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" t="s">
         <v>21</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" t="s">
         <v>22</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L2" t="s">
         <v>23</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="M2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="3" ht="18.75" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>25</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" t="s">
         <v>28</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1" t="s">
+      <c r="M3" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" t="s">
         <v>31</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" t="s">
         <v>32</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" t="s">
         <v>33</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" t="s">
         <v>34</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" t="s">
         <v>35</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" t="s">
         <v>36</v>
       </c>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1" t="s">
+      <c r="M4" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" t="s">
         <v>39</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" t="s">
         <v>40</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" t="s">
         <v>41</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" t="s">
         <v>35</v>
       </c>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1" t="s">
+      <c r="H5" t="s">
         <v>19</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="I5" t="s">
         <v>20</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="J5" t="s">
         <v>21</v>
       </c>
-      <c r="K5" s="1" t="s">
+      <c r="K5" t="s">
         <v>22</v>
       </c>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1" t="s">
+      <c r="M5" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="6" ht="18.75" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" t="s">
         <v>40</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1" t="s">
+      <c r="H6" t="s">
         <v>43</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="I6" t="s">
         <v>43</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="J6" t="s">
         <v>43</v>
       </c>
-      <c r="K6" s="1" t="s">
+      <c r="K6" t="s">
         <v>22</v>
       </c>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1" t="s">
+      <c r="M6" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="7" ht="18.75" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>44</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" t="s">
         <v>45</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" t="s">
         <v>46</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" t="s">
         <v>47</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" t="s">
         <v>18</v>
       </c>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1" t="s">
+      <c r="H7" t="s">
         <v>48</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="I7" t="s">
         <v>20</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="J7" t="s">
         <v>49</v>
       </c>
-      <c r="K7" s="1" t="s">
+      <c r="K7" t="s">
         <v>22</v>
       </c>
-      <c r="L7" s="1" t="s">
+      <c r="L7" t="s">
         <v>50</v>
       </c>
-      <c r="M7" s="1" t="s">
+      <c r="M7" t="s">
         <v>29</v>
       </c>
     </row>
@@ -914,72 +902,69 @@
   <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.862142857142857" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15.576428571428572" style="1" customWidth="1"/>
-    <col min="3" max="4" width="18.433571428571426" style="1" customWidth="1"/>
+    <col min="1" max="1" width="19.862142857142857" customWidth="1"/>
+    <col min="2" max="2" width="15.576428571428572" customWidth="1"/>
+    <col min="3" max="4" width="18.433571428571426" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>51</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>52</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>53</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>55</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>56</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>57</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="3" ht="18.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>59</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" t="s">
         <v>60</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s">
         <v>61</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="4" ht="18.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+    <row r="4" ht="18.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>43</v>
       </c>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>63</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" t="s">
         <v>64</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" t="s">
         <v>65</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" t="s">
         <v>66</v>
       </c>
     </row>
@@ -999,21 +984,21 @@
   <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.576428571428572" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.576428571428572" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="3" ht="18.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>68</v>
       </c>
     </row>
@@ -1024,7 +1009,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1067,8 +1052,48 @@
         <v>17</v>
       </c>
     </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F4" t="s">
+        <v>47</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/data/inventario.xlsx
+++ b/data/inventario.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="78">
   <si>
     <t>ID Pedido</t>
   </si>
@@ -148,9 +148,21 @@
     <t>6</t>
   </si>
   <si>
+    <t>Naportec</t>
+  </si>
+  <si>
+    <t>Quito</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
     <t>X CONFIRMAR</t>
   </si>
   <si>
+    <t>06:00</t>
+  </si>
+  <si>
     <t>7</t>
   </si>
   <si>
@@ -236,6 +248,9 @@
   </si>
   <si>
     <t>Gye-Cuenca</t>
+  </si>
+  <si>
+    <t>Gye-Quito</t>
   </si>
 </sst>
 </file>
@@ -824,63 +839,69 @@
         <v>40</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="E6" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="F6" t="s">
         <v>18</v>
       </c>
+      <c r="G6" t="s">
+        <v>45</v>
+      </c>
       <c r="H6" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="I6" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="J6" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K6" t="s">
         <v>22</v>
       </c>
+      <c r="L6" t="s">
+        <v>47</v>
+      </c>
       <c r="M6" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" ht="18.75" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D7" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E7" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F7" t="s">
         <v>18</v>
       </c>
       <c r="H7" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="I7" t="s">
         <v>20</v>
       </c>
       <c r="J7" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="K7" t="s">
         <v>22</v>
       </c>
       <c r="L7" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="M7" t="s">
         <v>29</v>
@@ -909,63 +930,63 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C1" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D1" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" ht="18.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B3" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D3" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D5" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -989,7 +1010,7 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -999,7 +1020,7 @@
     </row>
     <row r="3" ht="18.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -1009,7 +1030,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1020,7 +1041,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D1" t="s">
         <v>2</v>
@@ -1040,7 +1061,7 @@
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D2" t="s">
         <v>15</v>
@@ -1060,7 +1081,7 @@
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D3" t="s">
         <v>15</v>
@@ -1074,22 +1095,42 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D4" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E4" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F4" t="s">
-        <v>47</v>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D5" t="s">
+        <v>40</v>
+      </c>
+      <c r="E5" t="s">
+        <v>43</v>
+      </c>
+      <c r="F5" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/data/inventario.xlsx
+++ b/data/inventario.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="82">
   <si>
     <t>ID Pedido</t>
   </si>
@@ -67,190 +67,202 @@
     <t>ASUS</t>
   </si>
   <si>
+    <t>Unilever</t>
+  </si>
+  <si>
+    <t>Ambato</t>
+  </si>
+  <si>
+    <t>Externa</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>oscar</t>
+  </si>
+  <si>
+    <t>Juan Perez</t>
+  </si>
+  <si>
+    <t>david</t>
+  </si>
+  <si>
+    <t>GPR-1234</t>
+  </si>
+  <si>
+    <t>14:00</t>
+  </si>
+  <si>
+    <t>EN PROCESO</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>TESTEDIT</t>
+  </si>
+  <si>
+    <t>LUGAR X2</t>
+  </si>
+  <si>
+    <t>DEST2</t>
+  </si>
+  <si>
+    <t>PENDIENTE</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>2026-03-26</t>
+  </si>
+  <si>
+    <t>TESTE2</t>
+  </si>
+  <si>
+    <t>LUG2X</t>
+  </si>
+  <si>
+    <t>D2X</t>
+  </si>
+  <si>
+    <t>Interna</t>
+  </si>
+  <si>
+    <t>456</t>
+  </si>
+  <si>
+    <t>FINALIZADO</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>2026-03-25</t>
+  </si>
+  <si>
+    <t>REVIT</t>
+  </si>
+  <si>
     <t>GYE</t>
   </si>
   <si>
+    <t>BODEGA DAULE</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>Naportec</t>
+  </si>
+  <si>
+    <t>Quito</t>
+  </si>
+  <si>
+    <t>X CONFIRMAR</t>
+  </si>
+  <si>
+    <t>06:00</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>CARGOLAN</t>
+  </si>
+  <si>
+    <t>Contecon</t>
+  </si>
+  <si>
+    <t>Cuenca</t>
+  </si>
+  <si>
+    <t>Oscar Guachamin</t>
+  </si>
+  <si>
+    <t>David Sanchez</t>
+  </si>
+  <si>
+    <t>03:00</t>
+  </si>
+  <si>
+    <t>Nombre</t>
+  </si>
+  <si>
+    <t>Apellidos</t>
+  </si>
+  <si>
+    <t>CI</t>
+  </si>
+  <si>
+    <t>Telefono</t>
+  </si>
+  <si>
+    <t>Juan</t>
+  </si>
+  <si>
+    <t>Perez</t>
+  </si>
+  <si>
+    <t>0123456789</t>
+  </si>
+  <si>
+    <t>7894561230</t>
+  </si>
+  <si>
+    <t>David</t>
+  </si>
+  <si>
+    <t>Sanchez</t>
+  </si>
+  <si>
+    <t>9632587410</t>
+  </si>
+  <si>
+    <t>7410258963</t>
+  </si>
+  <si>
+    <t>Oscar</t>
+  </si>
+  <si>
+    <t>Guachamin</t>
+  </si>
+  <si>
+    <t>0923522866</t>
+  </si>
+  <si>
+    <t>0961142511</t>
+  </si>
+  <si>
+    <t>Placa</t>
+  </si>
+  <si>
+    <t>GTR-4569</t>
+  </si>
+  <si>
+    <t>Ruta</t>
+  </si>
+  <si>
+    <t>RUTA-PRUEBA</t>
+  </si>
+  <si>
     <t>UIO</t>
   </si>
   <si>
-    <t>Externa</t>
-  </si>
-  <si>
-    <t>oscar</t>
-  </si>
-  <si>
-    <t>Juan Perez</t>
-  </si>
-  <si>
-    <t>david</t>
-  </si>
-  <si>
-    <t>GPR-1234</t>
-  </si>
-  <si>
-    <t>14:00</t>
-  </si>
-  <si>
-    <t>EN PROCESO</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>TESTEDIT</t>
-  </si>
-  <si>
-    <t>LUGAR X2</t>
-  </si>
-  <si>
-    <t>DEST2</t>
-  </si>
-  <si>
-    <t>PENDIENTE</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>2026-03-26</t>
-  </si>
-  <si>
-    <t>TESTE2</t>
-  </si>
-  <si>
-    <t>LUG2X</t>
-  </si>
-  <si>
-    <t>D2X</t>
-  </si>
-  <si>
-    <t>Interna</t>
-  </si>
-  <si>
-    <t>456</t>
-  </si>
-  <si>
-    <t>FINALIZADO</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>2026-03-25</t>
-  </si>
-  <si>
-    <t>REVIT</t>
-  </si>
-  <si>
-    <t>BODEGA DAULE</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>Naportec</t>
-  </si>
-  <si>
-    <t>Quito</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>X CONFIRMAR</t>
-  </si>
-  <si>
-    <t>06:00</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>CARGOLAN</t>
+    <t>RUTA-PRUEBA-AUTO</t>
+  </si>
+  <si>
+    <t>Gye-Cuenca</t>
   </si>
   <si>
     <t>Pto.Contecom</t>
   </si>
   <si>
-    <t>Cuenca</t>
-  </si>
-  <si>
-    <t>Oscar Guachamin</t>
-  </si>
-  <si>
-    <t>David Sanchez</t>
-  </si>
-  <si>
-    <t>03:00</t>
-  </si>
-  <si>
-    <t>Nombre</t>
-  </si>
-  <si>
-    <t>Apellidos</t>
-  </si>
-  <si>
-    <t>CI</t>
-  </si>
-  <si>
-    <t>Telefono</t>
-  </si>
-  <si>
-    <t>Juan</t>
-  </si>
-  <si>
-    <t>Perez</t>
-  </si>
-  <si>
-    <t>0123456789</t>
-  </si>
-  <si>
-    <t>7894561230</t>
-  </si>
-  <si>
-    <t>David</t>
-  </si>
-  <si>
-    <t>Sanchez</t>
-  </si>
-  <si>
-    <t>9632587410</t>
-  </si>
-  <si>
-    <t>7410258963</t>
-  </si>
-  <si>
-    <t>Oscar</t>
-  </si>
-  <si>
-    <t>Guachamin</t>
-  </si>
-  <si>
-    <t>0923522866</t>
-  </si>
-  <si>
-    <t>0961142511</t>
-  </si>
-  <si>
-    <t>Placa</t>
-  </si>
-  <si>
-    <t>GTR-4569</t>
-  </si>
-  <si>
-    <t>Ruta</t>
-  </si>
-  <si>
-    <t>RUTA-PRUEBA</t>
-  </si>
-  <si>
-    <t>RUTA-PRUEBA-AUTO</t>
-  </si>
-  <si>
-    <t>Gye-Cuenca</t>
-  </si>
-  <si>
     <t>Gye-Quito</t>
+  </si>
+  <si>
+    <t>Gye-Ambato</t>
   </si>
 </sst>
 </file>
@@ -725,186 +737,192 @@
       <c r="F2" t="s">
         <v>18</v>
       </c>
+      <c r="G2" t="s">
+        <v>19</v>
+      </c>
       <c r="H2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" ht="18.75" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F3" t="s">
         <v>18</v>
       </c>
       <c r="M3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5" t="s">
+        <v>43</v>
+      </c>
+      <c r="F5" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J5" t="s">
+        <v>22</v>
+      </c>
+      <c r="K5" t="s">
+        <v>23</v>
+      </c>
+      <c r="M5" t="s">
         <v>38</v>
-      </c>
-      <c r="B5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C5" t="s">
-        <v>40</v>
-      </c>
-      <c r="D5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F5" t="s">
-        <v>35</v>
-      </c>
-      <c r="H5" t="s">
-        <v>19</v>
-      </c>
-      <c r="I5" t="s">
-        <v>20</v>
-      </c>
-      <c r="J5" t="s">
-        <v>21</v>
-      </c>
-      <c r="K5" t="s">
-        <v>22</v>
-      </c>
-      <c r="M5" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="6" ht="18.75" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F6" t="s">
         <v>18</v>
       </c>
       <c r="G6" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="H6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" ht="18.75" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F7" t="s">
         <v>18</v>
       </c>
+      <c r="G7" t="s">
+        <v>19</v>
+      </c>
       <c r="H7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -930,63 +948,63 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" ht="18.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -1010,17 +1028,17 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" ht="18.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -1030,7 +1048,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1041,7 +1059,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D1" t="s">
         <v>2</v>
@@ -1061,16 +1079,16 @@
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D2" t="s">
         <v>15</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="F2" t="s">
-        <v>17</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -1081,56 +1099,76 @@
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D3" t="s">
         <v>15</v>
       </c>
       <c r="E3" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="F3" t="s">
-        <v>17</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E4" t="s">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="F4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F5" t="s">
-        <v>44</v>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>81</v>
+      </c>
+      <c r="D6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/data/inventario.xlsx
+++ b/data/inventario.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="82">
   <si>
     <t>ID Pedido</t>
   </si>
@@ -100,13 +100,13 @@
     <t>3</t>
   </si>
   <si>
-    <t>TESTEDIT</t>
-  </si>
-  <si>
-    <t>LUGAR X2</t>
-  </si>
-  <si>
-    <t>DEST2</t>
+    <t>PORTRANS</t>
+  </si>
+  <si>
+    <t>Portrans</t>
+  </si>
+  <si>
+    <t>Santo Domingo</t>
   </si>
   <si>
     <t>PENDIENTE</t>
@@ -121,10 +121,7 @@
     <t>TESTE2</t>
   </si>
   <si>
-    <t>LUG2X</t>
-  </si>
-  <si>
-    <t>D2X</t>
+    <t>Balao</t>
   </si>
   <si>
     <t>Interna</t>
@@ -263,6 +260,9 @@
   </si>
   <si>
     <t>Gye-Ambato</t>
+  </si>
+  <si>
+    <t>Portrans-Santo Domingo</t>
   </si>
 </sst>
 </file>
@@ -778,6 +778,12 @@
       <c r="F3" t="s">
         <v>18</v>
       </c>
+      <c r="G3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L3" t="s">
+        <v>19</v>
+      </c>
       <c r="M3" t="s">
         <v>30</v>
       </c>
@@ -793,39 +799,42 @@
         <v>33</v>
       </c>
       <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" t="s">
         <v>34</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>35</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>36</v>
       </c>
-      <c r="G4" t="s">
+      <c r="L4" t="s">
+        <v>19</v>
+      </c>
+      <c r="M4" t="s">
         <v>37</v>
-      </c>
-      <c r="M4" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" t="s">
         <v>39</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>40</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>41</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>42</v>
       </c>
-      <c r="E5" t="s">
-        <v>43</v>
-      </c>
       <c r="F5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H5" t="s">
         <v>20</v>
@@ -840,24 +849,24 @@
         <v>23</v>
       </c>
       <c r="M5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" ht="18.75" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" t="s">
         <v>44</v>
       </c>
-      <c r="B6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C6" t="s">
-        <v>41</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>45</v>
-      </c>
-      <c r="E6" t="s">
-        <v>46</v>
       </c>
       <c r="F6" t="s">
         <v>18</v>
@@ -866,19 +875,19 @@
         <v>19</v>
       </c>
       <c r="H6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K6" t="s">
         <v>23</v>
       </c>
       <c r="L6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="M6" t="s">
         <v>25</v>
@@ -886,19 +895,19 @@
     </row>
     <row r="7" ht="18.75" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D7" t="s">
         <v>50</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>51</v>
-      </c>
-      <c r="E7" t="s">
-        <v>52</v>
       </c>
       <c r="F7" t="s">
         <v>18</v>
@@ -907,19 +916,19 @@
         <v>19</v>
       </c>
       <c r="H7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I7" t="s">
         <v>21</v>
       </c>
       <c r="J7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="K7" t="s">
         <v>23</v>
       </c>
       <c r="L7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M7" t="s">
         <v>30</v>
@@ -948,63 +957,63 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" t="s">
         <v>56</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>57</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>58</v>
-      </c>
-      <c r="D1" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B2" t="s">
         <v>60</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>61</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>62</v>
-      </c>
-      <c r="D2" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="3" ht="18.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B3" t="s">
         <v>64</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>65</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>66</v>
-      </c>
-      <c r="D3" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B5" t="s">
         <v>68</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>69</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>70</v>
-      </c>
-      <c r="D5" t="s">
-        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -1028,7 +1037,7 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -1038,7 +1047,7 @@
     </row>
     <row r="3" ht="18.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -1048,7 +1057,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1059,7 +1068,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D1" t="s">
         <v>2</v>
@@ -1079,16 +1088,16 @@
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D2" t="s">
         <v>15</v>
       </c>
       <c r="E2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -1099,56 +1108,56 @@
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D3" t="s">
         <v>15</v>
       </c>
       <c r="E3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E4" t="s">
         <v>78</v>
       </c>
-      <c r="D4" t="s">
-        <v>50</v>
-      </c>
-      <c r="E4" t="s">
-        <v>79</v>
-      </c>
       <c r="F4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E5" t="s">
+        <v>44</v>
+      </c>
+      <c r="F5" t="s">
         <v>45</v>
-      </c>
-      <c r="F5" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -1159,7 +1168,7 @@
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D6" t="s">
         <v>15</v>
@@ -1169,6 +1178,26 @@
       </c>
       <c r="F6" t="s">
         <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
+        <v>81</v>
+      </c>
+      <c r="D7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F7" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
